--- a/Data/Rules/InClover Rules Matrix.xlsx
+++ b/Data/Rules/InClover Rules Matrix.xlsx
@@ -748,10 +748,10 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -769,7 +769,7 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z2" t="b">
         <v>0</v>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="R3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z3" t="b">
         <v>0</v>
@@ -989,13 +989,13 @@
         <v>3</v>
       </c>
       <c r="Q4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -1028,10 +1028,10 @@
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF4" t="b">
         <v>0</v>
@@ -1114,10 +1114,10 @@
         <v>0</v>
       </c>
       <c r="R5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z5" t="b">
         <v>0</v>
@@ -1236,10 +1236,10 @@
         <v>0</v>
       </c>
       <c r="R6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -1257,7 +1257,7 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z6" t="b">
         <v>0</v>
@@ -1358,10 +1358,10 @@
         <v>0</v>
       </c>
       <c r="R7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -1379,7 +1379,7 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z7" t="b">
         <v>0</v>
@@ -1480,10 +1480,10 @@
         <v>0</v>
       </c>
       <c r="R8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -1501,7 +1501,7 @@
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z8" t="b">
         <v>0</v>
@@ -1602,10 +1602,10 @@
         <v>0</v>
       </c>
       <c r="R9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -1623,7 +1623,7 @@
         <v>2</v>
       </c>
       <c r="Y9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z9" t="b">
         <v>0</v>
@@ -1724,10 +1724,10 @@
         <v>0</v>
       </c>
       <c r="R10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -1846,10 +1846,10 @@
         <v>0</v>
       </c>
       <c r="R11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T11" t="b">
         <v>0</v>
@@ -1882,10 +1882,10 @@
         <v>0</v>
       </c>
       <c r="AD11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF11" t="b">
         <v>0</v>
@@ -2004,10 +2004,10 @@
         <v>0</v>
       </c>
       <c r="AD12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="b">
         <v>0</v>
@@ -2087,13 +2087,13 @@
         <v>3</v>
       </c>
       <c r="Q13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T13" t="b">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="AD13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="b">
         <v>0</v>
@@ -2170,106 +2170,106 @@
         <v>74</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K14" t="b">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="M14">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="N14" t="b">
         <v>0</v>
       </c>
       <c r="O14">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="P14">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="Q14" t="b">
         <v>0</v>
       </c>
       <c r="R14">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="S14">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="T14" t="b">
         <v>0</v>
       </c>
       <c r="U14">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="V14">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="W14" t="b">
         <v>0</v>
       </c>
       <c r="X14">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="Y14">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="Z14" t="b">
         <v>0</v>
       </c>
       <c r="AA14">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="AB14">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="AC14" t="b">
         <v>0</v>
       </c>
       <c r="AD14">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="AE14">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="AF14" t="b">
         <v>0</v>
       </c>
       <c r="AG14">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="AH14">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="AI14" t="b">
         <v>0</v>
       </c>
       <c r="AJ14">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="AK14">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="AL14" t="b">
         <v>1</v>
@@ -2334,10 +2334,10 @@
         <v>0</v>
       </c>
       <c r="R15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T15" t="b">
         <v>0</v>
@@ -2355,7 +2355,7 @@
         <v>2</v>
       </c>
       <c r="Y15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z15" t="b">
         <v>0</v>
@@ -2492,10 +2492,10 @@
         <v>0</v>
       </c>
       <c r="AD16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="b">
         <v>0</v>
@@ -2614,10 +2614,10 @@
         <v>0</v>
       </c>
       <c r="AD17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="b">
         <v>0</v>
@@ -2736,10 +2736,10 @@
         <v>0</v>
       </c>
       <c r="AD18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF18" t="b">
         <v>0</v>

--- a/Data/Rules/InClover Rules Matrix.xlsx
+++ b/Data/Rules/InClover Rules Matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="76">
   <si>
     <t>SKU</t>
   </si>
@@ -134,6 +134,9 @@
   </si>
   <si>
     <t>HQ_Max</t>
+  </si>
+  <si>
+    <t>Total Max</t>
   </si>
   <si>
     <t>25486</t>
@@ -570,10 +573,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AN18"/>
+  <dimension ref="A1:AO18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:40">
+    <row r="1" spans="1:41">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -694,16 +697,19 @@
       <c r="AN1" t="s">
         <v>39</v>
       </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="2" spans="1:40">
+    <row r="2" spans="1:41">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -816,16 +822,19 @@
       <c r="AN2">
         <v>0</v>
       </c>
+      <c r="AO2">
+        <v>32</v>
+      </c>
     </row>
-    <row r="3" spans="1:40">
+    <row r="3" spans="1:41">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -938,16 +947,19 @@
       <c r="AN3">
         <v>0</v>
       </c>
+      <c r="AO3">
+        <v>32</v>
+      </c>
     </row>
-    <row r="4" spans="1:40">
+    <row r="4" spans="1:41">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1060,16 +1072,19 @@
       <c r="AN4">
         <v>0</v>
       </c>
+      <c r="AO4">
+        <v>28</v>
+      </c>
     </row>
-    <row r="5" spans="1:40">
+    <row r="5" spans="1:41">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1182,16 +1197,19 @@
       <c r="AN5">
         <v>0</v>
       </c>
+      <c r="AO5">
+        <v>32</v>
+      </c>
     </row>
-    <row r="6" spans="1:40">
+    <row r="6" spans="1:41">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1304,16 +1322,19 @@
       <c r="AN6">
         <v>0</v>
       </c>
+      <c r="AO6">
+        <v>32</v>
+      </c>
     </row>
-    <row r="7" spans="1:40">
+    <row r="7" spans="1:41">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1426,16 +1447,19 @@
       <c r="AN7">
         <v>0</v>
       </c>
+      <c r="AO7">
+        <v>32</v>
+      </c>
     </row>
-    <row r="8" spans="1:40">
+    <row r="8" spans="1:41">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1548,16 +1572,19 @@
       <c r="AN8">
         <v>0</v>
       </c>
+      <c r="AO8">
+        <v>32</v>
+      </c>
     </row>
-    <row r="9" spans="1:40">
+    <row r="9" spans="1:41">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1670,16 +1697,19 @@
       <c r="AN9">
         <v>0</v>
       </c>
+      <c r="AO9">
+        <v>32</v>
+      </c>
     </row>
-    <row r="10" spans="1:40">
+    <row r="10" spans="1:41">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1792,16 +1822,19 @@
       <c r="AN10">
         <v>0</v>
       </c>
+      <c r="AO10">
+        <v>31</v>
+      </c>
     </row>
-    <row r="11" spans="1:40">
+    <row r="11" spans="1:41">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1914,16 +1947,19 @@
       <c r="AN11">
         <v>0</v>
       </c>
+      <c r="AO11">
+        <v>30</v>
+      </c>
     </row>
-    <row r="12" spans="1:40">
+    <row r="12" spans="1:41">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -2036,16 +2072,19 @@
       <c r="AN12">
         <v>0</v>
       </c>
+      <c r="AO12">
+        <v>31</v>
+      </c>
     </row>
-    <row r="13" spans="1:40">
+    <row r="13" spans="1:41">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -2158,16 +2197,19 @@
       <c r="AN13">
         <v>0</v>
       </c>
+      <c r="AO13">
+        <v>28</v>
+      </c>
     </row>
-    <row r="14" spans="1:40">
+    <row r="14" spans="1:41">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D14">
         <v>60</v>
@@ -2280,16 +2322,19 @@
       <c r="AN14">
         <v>0</v>
       </c>
+      <c r="AO14">
+        <v>660</v>
+      </c>
     </row>
-    <row r="15" spans="1:40">
+    <row r="15" spans="1:41">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -2402,260 +2447,269 @@
       <c r="AN15">
         <v>0</v>
       </c>
+      <c r="AO15">
+        <v>32</v>
+      </c>
     </row>
-    <row r="16" spans="1:40">
+    <row r="16" spans="1:41">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16">
+        <v>3</v>
+      </c>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>2</v>
+      </c>
+      <c r="J16">
+        <v>3</v>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>2</v>
+      </c>
+      <c r="M16">
+        <v>3</v>
+      </c>
+      <c r="N16" t="b">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>2</v>
+      </c>
+      <c r="P16">
+        <v>3</v>
+      </c>
+      <c r="Q16" t="b">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>2</v>
+      </c>
+      <c r="S16">
+        <v>3</v>
+      </c>
+      <c r="T16" t="b">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>2</v>
+      </c>
+      <c r="V16">
+        <v>3</v>
+      </c>
+      <c r="W16" t="b">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>2</v>
+      </c>
+      <c r="Y16">
+        <v>3</v>
+      </c>
+      <c r="Z16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>2</v>
+      </c>
+      <c r="AB16">
+        <v>3</v>
+      </c>
+      <c r="AC16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>1</v>
+      </c>
+      <c r="AE16">
+        <v>2</v>
+      </c>
+      <c r="AF16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>2</v>
+      </c>
+      <c r="AH16">
+        <v>3</v>
+      </c>
+      <c r="AI16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>1</v>
+      </c>
+      <c r="AK16">
+        <v>2</v>
+      </c>
+      <c r="AL16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:41">
+      <c r="A17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17" t="b">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17">
+        <v>3</v>
+      </c>
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>2</v>
+      </c>
+      <c r="J17">
+        <v>3</v>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>2</v>
+      </c>
+      <c r="M17">
+        <v>3</v>
+      </c>
+      <c r="N17" t="b">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>2</v>
+      </c>
+      <c r="P17">
+        <v>3</v>
+      </c>
+      <c r="Q17" t="b">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>2</v>
+      </c>
+      <c r="S17">
+        <v>3</v>
+      </c>
+      <c r="T17" t="b">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>2</v>
+      </c>
+      <c r="V17">
+        <v>3</v>
+      </c>
+      <c r="W17" t="b">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>2</v>
+      </c>
+      <c r="Y17">
+        <v>3</v>
+      </c>
+      <c r="Z17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>2</v>
+      </c>
+      <c r="AB17">
+        <v>3</v>
+      </c>
+      <c r="AC17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>1</v>
+      </c>
+      <c r="AE17">
+        <v>2</v>
+      </c>
+      <c r="AF17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>2</v>
+      </c>
+      <c r="AH17">
+        <v>3</v>
+      </c>
+      <c r="AI17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <v>1</v>
+      </c>
+      <c r="AK17">
+        <v>2</v>
+      </c>
+      <c r="AL17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:41">
+      <c r="A18" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" t="s">
         <v>74</v>
       </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16" t="b">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>2</v>
-      </c>
-      <c r="G16">
-        <v>3</v>
-      </c>
-      <c r="H16" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>2</v>
-      </c>
-      <c r="J16">
-        <v>3</v>
-      </c>
-      <c r="K16" t="b">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>2</v>
-      </c>
-      <c r="M16">
-        <v>3</v>
-      </c>
-      <c r="N16" t="b">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>2</v>
-      </c>
-      <c r="P16">
-        <v>3</v>
-      </c>
-      <c r="Q16" t="b">
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>2</v>
-      </c>
-      <c r="S16">
-        <v>3</v>
-      </c>
-      <c r="T16" t="b">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>2</v>
-      </c>
-      <c r="V16">
-        <v>3</v>
-      </c>
-      <c r="W16" t="b">
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <v>2</v>
-      </c>
-      <c r="Y16">
-        <v>3</v>
-      </c>
-      <c r="Z16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA16">
-        <v>2</v>
-      </c>
-      <c r="AB16">
-        <v>3</v>
-      </c>
-      <c r="AC16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD16">
-        <v>1</v>
-      </c>
-      <c r="AE16">
-        <v>2</v>
-      </c>
-      <c r="AF16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16">
-        <v>2</v>
-      </c>
-      <c r="AH16">
-        <v>3</v>
-      </c>
-      <c r="AI16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ16">
-        <v>1</v>
-      </c>
-      <c r="AK16">
-        <v>2</v>
-      </c>
-      <c r="AL16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM16">
-        <v>0</v>
-      </c>
-      <c r="AN16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:40">
-      <c r="A17" t="s">
-        <v>55</v>
-      </c>
-      <c r="B17" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" t="s">
-        <v>74</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17" t="b">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>2</v>
-      </c>
-      <c r="G17">
-        <v>3</v>
-      </c>
-      <c r="H17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>2</v>
-      </c>
-      <c r="J17">
-        <v>3</v>
-      </c>
-      <c r="K17" t="b">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>2</v>
-      </c>
-      <c r="M17">
-        <v>3</v>
-      </c>
-      <c r="N17" t="b">
-        <v>0</v>
-      </c>
-      <c r="O17">
-        <v>2</v>
-      </c>
-      <c r="P17">
-        <v>3</v>
-      </c>
-      <c r="Q17" t="b">
-        <v>0</v>
-      </c>
-      <c r="R17">
-        <v>2</v>
-      </c>
-      <c r="S17">
-        <v>3</v>
-      </c>
-      <c r="T17" t="b">
-        <v>0</v>
-      </c>
-      <c r="U17">
-        <v>2</v>
-      </c>
-      <c r="V17">
-        <v>3</v>
-      </c>
-      <c r="W17" t="b">
-        <v>0</v>
-      </c>
-      <c r="X17">
-        <v>2</v>
-      </c>
-      <c r="Y17">
-        <v>3</v>
-      </c>
-      <c r="Z17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA17">
-        <v>2</v>
-      </c>
-      <c r="AB17">
-        <v>3</v>
-      </c>
-      <c r="AC17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD17">
-        <v>1</v>
-      </c>
-      <c r="AE17">
-        <v>2</v>
-      </c>
-      <c r="AF17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17">
-        <v>2</v>
-      </c>
-      <c r="AH17">
-        <v>3</v>
-      </c>
-      <c r="AI17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ17">
-        <v>1</v>
-      </c>
-      <c r="AK17">
-        <v>2</v>
-      </c>
-      <c r="AL17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM17">
-        <v>0</v>
-      </c>
-      <c r="AN17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:40">
-      <c r="A18" t="s">
-        <v>56</v>
-      </c>
-      <c r="B18" t="s">
-        <v>73</v>
-      </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -2709,10 +2763,10 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W18" t="b">
         <v>0</v>
@@ -2767,6 +2821,9 @@
       </c>
       <c r="AN18">
         <v>0</v>
+      </c>
+      <c r="AO18">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
